--- a/output/pdf_financials_xlsx/WCN.xlsx
+++ b/output/pdf_financials_xlsx/WCN.xlsx
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-79.32599999999999</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -3739,15 +3739,11 @@
       <c r="C129" s="3" t="n">
         <v>-116.574</v>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>134.237</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-83.67100000000001</v>
       </c>
       <c r="F129" s="3" t="n">
         <v>-183.512</v>
@@ -3888,26 +3884,22 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>219.261</v>
+        <v>218.481</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>258.599</v>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>256.269</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>293.861</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>395.706</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>447.318</v>
+        <v>450.735</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>393.858</v>
+        <v>399.726</v>
       </c>
     </row>
   </sheetData>
@@ -9840,7 +9832,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -11884,7 +11880,11 @@
           <t>Repurchase of common shares (Note 18)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -12372,7 +12372,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E189" s="5" t="n">
         <v>218.481</v>
       </c>
